--- a/salidas/empresas/FIS.xlsx
+++ b/salidas/empresas/FIS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>16.02047348022461</v>
+        <v>16.02048301696777</v>
       </c>
       <c r="C2" t="n">
         <v>43.45000076293945</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.00030326843262</v>
+        <v>16.00030899047852</v>
       </c>
       <c r="C3" t="n">
         <v>39.65000152587891</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>16.38399887084961</v>
+        <v>16.38400077819824</v>
       </c>
       <c r="C4" t="n">
         <v>40.54999923706055</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>15.35368728637695</v>
+        <v>15.35368347167969</v>
       </c>
       <c r="C5" t="n">
         <v>38</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>14.84458351135254</v>
+        <v>14.84458637237549</v>
       </c>
       <c r="C6" t="n">
         <v>36.7400016784668</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>14.32334613800049</v>
+        <v>14.32334041595459</v>
       </c>
       <c r="C7" t="n">
         <v>35.40000152587891</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>14.46091556549072</v>
+        <v>14.46091842651367</v>
       </c>
       <c r="C8" t="n">
         <v>35.7400016784668</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.99108409881592</v>
+        <v>14.9910831451416</v>
       </c>
       <c r="C10" t="n">
         <v>37</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>16.84268379211426</v>
+        <v>16.84268569946289</v>
       </c>
       <c r="C11" t="n">
         <v>41.56999969482422</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>16.16606140136719</v>
+        <v>16.16607093811035</v>
       </c>
       <c r="C12" t="n">
         <v>39.90000152587891</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>16.26308822631836</v>
+        <v>16.26308631896973</v>
       </c>
       <c r="C13" t="n">
         <v>40.09000015258789</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>17.24885940551758</v>
+        <v>17.24885559082031</v>
       </c>
       <c r="C14" t="n">
         <v>42.52000045776367</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>18.62809753417969</v>
+        <v>18.62811279296875</v>
       </c>
       <c r="C15" t="n">
         <v>45.91999816894531</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>18.46187973022461</v>
+        <v>18.46187782287598</v>
       </c>
       <c r="C16" t="n">
         <v>45.45999908447266</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>20.52087783813477</v>
+        <v>20.5208740234375</v>
       </c>
       <c r="C17" t="n">
         <v>50.52999877929688</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>21.89760398864746</v>
+        <v>21.89759254455566</v>
       </c>
       <c r="C18" t="n">
         <v>53.91999816894531</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>22.0648021697998</v>
+        <v>22.06480598449707</v>
       </c>
       <c r="C19" t="n">
         <v>54.27999877929688</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>20.17457389831543</v>
+        <v>20.1745662689209</v>
       </c>
       <c r="C20" t="n">
         <v>49.63000106811523</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>19.26808547973633</v>
+        <v>19.26807975769043</v>
       </c>
       <c r="C21" t="n">
         <v>47.40000152587891</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>18.05658912658691</v>
+        <v>18.05658531188965</v>
       </c>
       <c r="C22" t="n">
         <v>44.36999893188477</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>18.75247764587402</v>
+        <v>18.75248336791992</v>
       </c>
       <c r="C23" t="n">
         <v>46.08000183105469</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>16.94396018981934</v>
+        <v>16.94395637512207</v>
       </c>
       <c r="C25" t="n">
         <v>41.59000015258789</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>17.28210639953613</v>
+        <v>17.28209495544434</v>
       </c>
       <c r="C26" t="n">
         <v>42.41999816894531</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.55872917175293</v>
+        <v>15.55872631072998</v>
       </c>
       <c r="C28" t="n">
         <v>38.13999938964844</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>14.71022033691406</v>
+        <v>14.71021842956543</v>
       </c>
       <c r="C29" t="n">
         <v>36.06000137329102</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>16.43170928955078</v>
+        <v>16.43171119689941</v>
       </c>
       <c r="C30" t="n">
         <v>40.27999877929688</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.07625770568848</v>
+        <v>15.07626152038574</v>
       </c>
       <c r="C31" t="n">
         <v>36.90999984741211</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>13.89526271820068</v>
+        <v>13.89526748657227</v>
       </c>
       <c r="C32" t="n">
         <v>18.95000076293945</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>16.02171325683594</v>
+        <v>16.02172660827637</v>
       </c>
       <c r="C33" t="n">
         <v>21.85000038146973</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>13.56740474700928</v>
+        <v>13.56740760803223</v>
       </c>
       <c r="C34" t="n">
         <v>18.45999908447266</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>11.09058284759521</v>
+        <v>11.09057712554932</v>
       </c>
       <c r="C35" t="n">
         <v>15.09000015258789</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>12.6266565322876</v>
+        <v>12.62665367126465</v>
       </c>
       <c r="C36" t="n">
         <v>17.18000030517578</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>11.9940071105957</v>
+        <v>11.99400806427002</v>
       </c>
       <c r="C37" t="n">
         <v>16.27000045776367</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.7286205291748</v>
+        <v>11.72861862182617</v>
       </c>
       <c r="C38" t="n">
         <v>15.90999984741211</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>13.45748138427734</v>
+        <v>13.45748329162598</v>
       </c>
       <c r="C40" t="n">
         <v>18.20000076293945</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>13.19867992401123</v>
+        <v>13.19868564605713</v>
       </c>
       <c r="C41" t="n">
         <v>17.85000038146973</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.24127197265625</v>
+        <v>14.24127292633057</v>
       </c>
       <c r="C42" t="n">
         <v>19.26000022888184</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.79530334472656</v>
+        <v>14.79530429840088</v>
       </c>
       <c r="C43" t="n">
         <v>19.95999908447266</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.36001777648926</v>
+        <v>17.36001968383789</v>
       </c>
       <c r="C44" t="n">
         <v>23.42000007629395</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>18.20503997802734</v>
+        <v>18.20504951477051</v>
       </c>
       <c r="C45" t="n">
         <v>24.55999946594238</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>18.94739723205566</v>
+        <v>18.94740676879883</v>
       </c>
       <c r="C46" t="n">
         <v>25.51000022888184</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.162109375</v>
+        <v>16.1621036529541</v>
       </c>
       <c r="C47" t="n">
         <v>21.76000022888184</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>16.78600883483887</v>
+        <v>16.78601837158203</v>
       </c>
       <c r="C48" t="n">
         <v>22.60000038146973</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.44668006896973</v>
+        <v>17.44668388366699</v>
       </c>
       <c r="C49" t="n">
         <v>23.44000053405762</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>17.53599739074707</v>
+        <v>17.53600120544434</v>
       </c>
       <c r="C50" t="n">
         <v>23.55999946594238</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.77680015563965</v>
+        <v>16.77679824829102</v>
       </c>
       <c r="C51" t="n">
         <v>22.54000091552734</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>17.4843635559082</v>
+        <v>17.48437118530273</v>
       </c>
       <c r="C52" t="n">
         <v>23.44000053405762</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>19.61023139953613</v>
+        <v>19.61023712158203</v>
       </c>
       <c r="C53" t="n">
         <v>26.29000091552734</v>
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>20.04239845275879</v>
+        <v>20.04239654541016</v>
       </c>
       <c r="C55" t="n">
         <v>26.81999969482422</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>21.42489624023438</v>
+        <v>21.42489051818848</v>
       </c>
       <c r="C56" t="n">
         <v>28.67000007629395</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>19.31753349304199</v>
+        <v>19.31752967834473</v>
       </c>
       <c r="C57" t="n">
         <v>25.85000038146973</v>
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>20.28830718994141</v>
+        <v>20.28830337524414</v>
       </c>
       <c r="C59" t="n">
         <v>27.10000038146973</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.13858222961426</v>
+        <v>20.13857650756836</v>
       </c>
       <c r="C60" t="n">
         <v>26.89999961853027</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.5423583984375</v>
+        <v>20.54236602783203</v>
       </c>
       <c r="C61" t="n">
         <v>27.38999938964844</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>22.82233810424805</v>
+        <v>22.82234191894531</v>
       </c>
       <c r="C62" t="n">
         <v>30.43000030517578</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>24.29233741760254</v>
+        <v>24.29232978820801</v>
       </c>
       <c r="C63" t="n">
         <v>32.38999938964844</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>24.55695343017578</v>
+        <v>24.55695724487305</v>
       </c>
       <c r="C64" t="n">
         <v>32.68999862670898</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>24.87246322631836</v>
+        <v>24.87245941162109</v>
       </c>
       <c r="C65" t="n">
         <v>33.11000061035156</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>24.17383575439453</v>
+        <v>24.17384338378906</v>
       </c>
       <c r="C66" t="n">
         <v>32.18000030517578</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>23.16655921936035</v>
+        <v>23.16656494140625</v>
       </c>
       <c r="C67" t="n">
         <v>30.79000091552734</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>22.58720970153809</v>
+        <v>22.58721351623535</v>
       </c>
       <c r="C68" t="n">
         <v>30.02000045776367</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>21.20279121398926</v>
+        <v>21.20278167724609</v>
       </c>
       <c r="C69" t="n">
         <v>28.18000030517578</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>18.33438110351562</v>
+        <v>18.33437728881836</v>
       </c>
       <c r="C70" t="n">
         <v>24.31999969482422</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.73660087585449</v>
+        <v>19.73660278320312</v>
       </c>
       <c r="C71" t="n">
         <v>26.18000030517578</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>18.16098022460938</v>
+        <v>18.16098594665527</v>
       </c>
       <c r="C72" t="n">
         <v>24.09000015258789</v>
@@ -2039,7 +2051,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2097,7 +2109,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2126,7 +2138,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>25.59317398071289</v>
+        <v>25.59317779541016</v>
       </c>
       <c r="C77" t="n">
         <v>33.66999816894531</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>24.91666412353516</v>
+        <v>24.91667556762695</v>
       </c>
       <c r="C78" t="n">
         <v>32.77999877929688</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>26.06723785400391</v>
+        <v>26.06722831726074</v>
       </c>
       <c r="C79" t="n">
         <v>34.08000183105469</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>24.04794883728027</v>
+        <v>24.04794692993164</v>
       </c>
       <c r="C80" t="n">
         <v>31.44000053405762</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>24.09383773803711</v>
+        <v>24.09384536743164</v>
       </c>
       <c r="C81" t="n">
         <v>31.5</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.03004264831543</v>
+        <v>24.03005027770996</v>
       </c>
       <c r="C82" t="n">
         <v>31.21999931335449</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.30005073547363</v>
+        <v>25.300048828125</v>
       </c>
       <c r="C83" t="n">
         <v>32.86999893188477</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>27.78617286682129</v>
+        <v>27.78618621826172</v>
       </c>
       <c r="C84" t="n">
         <v>36.09999847412109</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>26.94146919250488</v>
+        <v>26.94147109985352</v>
       </c>
       <c r="C85" t="n">
         <v>34.81000137329102</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>28.72156143188477</v>
+        <v>28.72156715393066</v>
       </c>
       <c r="C86" t="n">
         <v>37.11000061035156</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>29.13950157165527</v>
+        <v>29.13950538635254</v>
       </c>
       <c r="C87" t="n">
         <v>37.65000152587891</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>30.84050941467285</v>
+        <v>30.84051704406738</v>
       </c>
       <c r="C88" t="n">
         <v>39.61999893188477</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>33.51237487792969</v>
+        <v>33.51237869262695</v>
       </c>
       <c r="C91" t="n">
         <v>42.84000015258789</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>33.76271057128906</v>
+        <v>33.76270294189453</v>
       </c>
       <c r="C92" t="n">
         <v>43.15999984741211</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>34.77965927124023</v>
+        <v>34.77965545654297</v>
       </c>
       <c r="C93" t="n">
         <v>44.45999908447266</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>36.50373840332031</v>
+        <v>36.50372695922852</v>
       </c>
       <c r="C94" t="n">
         <v>46.43999862670898</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>38.31948471069336</v>
+        <v>38.31949615478516</v>
       </c>
       <c r="C95" t="n">
         <v>48.75</v>
@@ -2706,7 +2718,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>42.37929534912109</v>
+        <v>42.37929153442383</v>
       </c>
       <c r="C97" t="n">
         <v>53.68000030517578</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>40.02664566040039</v>
+        <v>40.02663803100586</v>
       </c>
       <c r="C98" t="n">
         <v>50.70000076293945</v>
@@ -2793,7 +2805,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>42.38351821899414</v>
+        <v>42.38351058959961</v>
       </c>
       <c r="C100" t="n">
         <v>53.45000076293945</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>42.3676643371582</v>
+        <v>42.36766815185547</v>
       </c>
       <c r="C101" t="n">
         <v>53.43000030517578</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>42.93857192993164</v>
+        <v>42.93857955932617</v>
       </c>
       <c r="C102" t="n">
         <v>54.15000152587891</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>43.59864807128906</v>
+        <v>43.59866333007812</v>
       </c>
       <c r="C103" t="n">
         <v>54.7400016784668</v>
@@ -2938,7 +2950,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>45.19955062866211</v>
+        <v>45.19956970214844</v>
       </c>
       <c r="C105" t="n">
         <v>56.75</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>45.02913284301758</v>
+        <v>45.02913665771484</v>
       </c>
       <c r="C106" t="n">
         <v>56.29999923706055</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>46.70072937011719</v>
+        <v>46.70071411132812</v>
       </c>
       <c r="C107" t="n">
         <v>58.38999938964844</v>
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>49.94453811645508</v>
+        <v>49.94453048706055</v>
       </c>
       <c r="C109" t="n">
         <v>62.20000076293945</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>50.12921142578125</v>
+        <v>50.12921524047852</v>
       </c>
       <c r="C110" t="n">
         <v>62.43000030517578</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.27252197265625</v>
+        <v>54.27250289916992</v>
       </c>
       <c r="C111" t="n">
         <v>67.58999633789062</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>54.86521911621094</v>
+        <v>54.865234375</v>
       </c>
       <c r="C112" t="n">
         <v>68.05999755859375</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>50.37510681152344</v>
+        <v>50.37508773803711</v>
       </c>
       <c r="C113" t="n">
         <v>62.4900016784668</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>50.54437255859375</v>
+        <v>50.54437637329102</v>
       </c>
       <c r="C114" t="n">
         <v>62.70000076293945</v>
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>52.95973205566406</v>
+        <v>52.9597282409668</v>
       </c>
       <c r="C116" t="n">
         <v>65.43000030517578</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>55.89787292480469</v>
+        <v>55.89786911010742</v>
       </c>
       <c r="C117" t="n">
         <v>69.05999755859375</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>54.49880218505859</v>
+        <v>54.49877548217773</v>
       </c>
       <c r="C118" t="n">
         <v>67.08000183105469</v>
@@ -3373,7 +3385,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>51.72834014892578</v>
+        <v>51.72834777832031</v>
       </c>
       <c r="C120" t="n">
         <v>63.66999816894531</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.4442024230957</v>
+        <v>49.44418334960938</v>
       </c>
       <c r="C121" t="n">
         <v>60.59999847412109</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>48.734375</v>
+        <v>48.73435592651367</v>
       </c>
       <c r="C122" t="n">
         <v>59.72999954223633</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>47.52681350708008</v>
+        <v>47.52680206298828</v>
       </c>
       <c r="C123" t="n">
         <v>58.25</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>51.87005996704102</v>
+        <v>51.87006378173828</v>
       </c>
       <c r="C124" t="n">
         <v>63.31000137329102</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>53.91013336181641</v>
+        <v>53.9101448059082</v>
       </c>
       <c r="C125" t="n">
         <v>65.80000305175781</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>60.84964370727539</v>
+        <v>60.849609375</v>
       </c>
       <c r="C126" t="n">
         <v>74.26999664306641</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>60.58069610595703</v>
+        <v>60.58073043823242</v>
       </c>
       <c r="C127" t="n">
         <v>73.68000030517578</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>65.39066314697266</v>
+        <v>65.39067840576172</v>
       </c>
       <c r="C128" t="n">
         <v>79.52999877929688</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>65.22621154785156</v>
+        <v>65.22621917724609</v>
       </c>
       <c r="C129" t="n">
         <v>79.33000183105469</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>63.55059432983398</v>
+        <v>63.55055236816406</v>
       </c>
       <c r="C130" t="n">
         <v>77.02999877929688</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>60.98478698730469</v>
+        <v>60.98480606079102</v>
       </c>
       <c r="C131" t="n">
         <v>73.91999816894531</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>63.68259048461914</v>
+        <v>63.68255996704102</v>
       </c>
       <c r="C132" t="n">
         <v>77.19000244140625</v>
@@ -3779,7 +3791,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>65.74924468994141</v>
+        <v>65.74928283691406</v>
       </c>
       <c r="C134" t="n">
         <v>79.41999816894531</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>68.10868072509766</v>
+        <v>68.10868835449219</v>
       </c>
       <c r="C135" t="n">
         <v>82.26999664306641</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>66.14748382568359</v>
+        <v>66.14746856689453</v>
       </c>
       <c r="C136" t="n">
         <v>79.62000274658203</v>
@@ -3895,7 +3907,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>71.33991241455078</v>
+        <v>71.33992767333984</v>
       </c>
       <c r="C138" t="n">
         <v>85.87000274658203</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>71.19020843505859</v>
+        <v>71.19021606445312</v>
       </c>
       <c r="C139" t="n">
         <v>85.40000152587891</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>76.04181671142578</v>
+        <v>76.04184722900391</v>
       </c>
       <c r="C140" t="n">
         <v>91.22000122070312</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>77.45894622802734</v>
+        <v>77.45893859863281</v>
       </c>
       <c r="C141" t="n">
         <v>92.91999816894531</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>78.09581756591797</v>
+        <v>78.09580993652344</v>
       </c>
       <c r="C142" t="n">
         <v>93.38999938964844</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>77.56897735595703</v>
+        <v>77.56898498535156</v>
       </c>
       <c r="C143" t="n">
         <v>92.76000213623047</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>78.88184356689453</v>
+        <v>78.88185882568359</v>
       </c>
       <c r="C144" t="n">
         <v>94.33000183105469</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.92395782470703</v>
+        <v>78.92399597167969</v>
       </c>
       <c r="C145" t="n">
         <v>94.08999633789062</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>85.86098480224609</v>
+        <v>85.86097717285156</v>
       </c>
       <c r="C146" t="n">
         <v>102.3600006103516</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>81.51589202880859</v>
+        <v>81.51591491699219</v>
       </c>
       <c r="C147" t="n">
         <v>97.18000030517578</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>81.03624725341797</v>
+        <v>81.03627014160156</v>
       </c>
       <c r="C148" t="n">
         <v>96.30000305175781</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>79.91706848144531</v>
+        <v>79.91706085205078</v>
       </c>
       <c r="C149" t="n">
         <v>94.97000122070312</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>86.01789855957031</v>
+        <v>86.01793670654297</v>
       </c>
       <c r="C150" t="n">
         <v>102.2200012207031</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>89.49141693115234</v>
+        <v>89.49140930175781</v>
       </c>
       <c r="C151" t="n">
         <v>106.0299987792969</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>87.04374694824219</v>
+        <v>87.04375457763672</v>
       </c>
       <c r="C152" t="n">
         <v>103.129997253418</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>91.29758453369141</v>
+        <v>91.29761505126953</v>
       </c>
       <c r="C153" t="n">
         <v>108.1699981689453</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>92.32704162597656</v>
+        <v>92.3270263671875</v>
       </c>
       <c r="C154" t="n">
         <v>109.0699996948242</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>88.11996459960938</v>
+        <v>88.11997985839844</v>
       </c>
       <c r="C155" t="n">
         <v>104.0999984741211</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>91.37899017333984</v>
+        <v>91.37896728515625</v>
       </c>
       <c r="C156" t="n">
         <v>107.9499969482422</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>87.06895446777344</v>
+        <v>87.06893157958984</v>
       </c>
       <c r="C157" t="n">
         <v>102.5500030517578</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>88.75003814697266</v>
+        <v>88.75001525878906</v>
       </c>
       <c r="C158" t="n">
         <v>104.5299987792969</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>91.82357788085938</v>
+        <v>91.82356262207031</v>
       </c>
       <c r="C159" t="n">
         <v>108.1500015258789</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>96.33966827392578</v>
+        <v>96.33966064453125</v>
       </c>
       <c r="C160" t="n">
         <v>113.0999984741211</v>
@@ -4591,7 +4603,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>102.4726791381836</v>
+        <v>102.4727020263672</v>
       </c>
       <c r="C162" t="n">
         <v>120.3000030517578</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>104.8032836914062</v>
+        <v>104.8032913208008</v>
       </c>
       <c r="C163" t="n">
         <v>122.6800003051758</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>113.8330230712891</v>
+        <v>113.8330307006836</v>
       </c>
       <c r="C164" t="n">
         <v>133.25</v>
@@ -4707,7 +4719,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>113.7176055908203</v>
+        <v>113.7175979614258</v>
       </c>
       <c r="C166" t="n">
         <v>132.7599945068359</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>112.8610305786133</v>
+        <v>112.8610382080078</v>
       </c>
       <c r="C167" t="n">
         <v>131.7599945068359</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>118.3344955444336</v>
+        <v>118.33447265625</v>
       </c>
       <c r="C168" t="n">
         <v>138.1499938964844</v>
@@ -4823,7 +4835,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>123.3728408813477</v>
+        <v>123.3728256225586</v>
       </c>
       <c r="C170" t="n">
         <v>143.6600036621094</v>
@@ -4881,7 +4893,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>104.7381286621094</v>
+        <v>104.7381439208984</v>
       </c>
       <c r="C172" t="n">
         <v>121.6399993896484</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>113.5638809204102</v>
+        <v>113.5638961791992</v>
       </c>
       <c r="C173" t="n">
         <v>131.8899993896484</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>119.5395660400391</v>
+        <v>119.5395736694336</v>
       </c>
       <c r="C174" t="n">
         <v>138.8300018310547</v>
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>126.2932281494141</v>
+        <v>126.2932586669922</v>
       </c>
       <c r="C176" t="n">
         <v>146.3099975585938</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>130.2121276855469</v>
+        <v>130.212158203125</v>
       </c>
       <c r="C177" t="n">
         <v>150.8500061035156</v>
@@ -5082,11 +5094,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>127.3703308105469</v>
+        <v>127.3703079223633</v>
       </c>
       <c r="C178" t="n">
         <v>147.2100067138672</v>
@@ -5109,11 +5121,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>107.798828125</v>
+        <v>107.7988357543945</v>
       </c>
       <c r="C179" t="n">
         <v>124.5899963378906</v>
@@ -5136,7 +5148,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5163,11 +5175,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>122.6864013671875</v>
+        <v>122.686408996582</v>
       </c>
       <c r="C181" t="n">
         <v>141.4600067138672</v>
@@ -5190,11 +5202,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>107.0752487182617</v>
+        <v>107.0752716064453</v>
       </c>
       <c r="C182" t="n">
         <v>123.4599990844727</v>
@@ -5217,7 +5229,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5246,7 +5258,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5275,7 +5287,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>129.5556640625</v>
+        <v>129.5556335449219</v>
       </c>
       <c r="C186" t="n">
         <v>148.9799957275391</v>
@@ -5331,11 +5343,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>123.5306930541992</v>
+        <v>123.5307159423828</v>
       </c>
       <c r="C187" t="n">
         <v>141.6699981689453</v>
@@ -5358,11 +5370,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>129.9657440185547</v>
+        <v>129.9657592773438</v>
       </c>
       <c r="C188" t="n">
         <v>149.0500030517578</v>
@@ -5385,11 +5397,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>111.4104232788086</v>
+        <v>111.4104385375977</v>
       </c>
       <c r="C189" t="n">
         <v>127.7699966430664</v>
@@ -5414,11 +5426,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>106.4194564819336</v>
+        <v>106.4194641113281</v>
       </c>
       <c r="C190" t="n">
         <v>121.6800003051758</v>
@@ -5443,11 +5455,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>96.85150146484375</v>
+        <v>96.85149383544922</v>
       </c>
       <c r="C191" t="n">
         <v>110.7399978637695</v>
@@ -5472,11 +5484,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>91.39409637451172</v>
+        <v>91.39411163330078</v>
       </c>
       <c r="C192" t="n">
         <v>104.5</v>
@@ -5501,11 +5513,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>95.81685638427734</v>
+        <v>95.81684875488281</v>
       </c>
       <c r="C193" t="n">
         <v>109.1500015258789</v>
@@ -5530,11 +5542,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>105.2712097167969</v>
+        <v>105.2712249755859</v>
       </c>
       <c r="C194" t="n">
         <v>119.9199981689453</v>
@@ -5559,11 +5571,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>83.59722900390625</v>
+        <v>83.59723663330078</v>
       </c>
       <c r="C195" t="n">
         <v>95.23000335693359</v>
@@ -5588,7 +5600,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5617,11 +5629,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>87.48539733886719</v>
+        <v>87.48541259765625</v>
       </c>
       <c r="C197" t="n">
         <v>99.15000152587891</v>
@@ -5646,11 +5658,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>92.20601654052734</v>
+        <v>92.20600891113281</v>
       </c>
       <c r="C198" t="n">
         <v>104.5</v>
@@ -5675,11 +5687,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>81.25344848632812</v>
+        <v>81.25347137451172</v>
       </c>
       <c r="C199" t="n">
         <v>91.66999816894531</v>
@@ -5704,11 +5716,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>90.55146789550781</v>
+        <v>90.55146026611328</v>
       </c>
       <c r="C200" t="n">
         <v>102.1600036621094</v>
@@ -5733,7 +5745,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5762,11 +5774,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>67.34648132324219</v>
+        <v>67.34648895263672</v>
       </c>
       <c r="C202" t="n">
         <v>75.56999969482422</v>
@@ -5791,11 +5803,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>73.95903778076172</v>
+        <v>73.95904541015625</v>
       </c>
       <c r="C203" t="n">
         <v>82.98999786376953</v>
@@ -5820,7 +5832,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5849,11 +5861,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>60.87989807128906</v>
+        <v>60.87988662719727</v>
       </c>
       <c r="C205" t="n">
         <v>67.84999847412109</v>
@@ -5878,11 +5890,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>67.33127593994141</v>
+        <v>67.33126831054688</v>
       </c>
       <c r="C206" t="n">
         <v>75.04000091552734</v>
@@ -5907,11 +5919,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>56.860107421875</v>
+        <v>56.86010360717773</v>
       </c>
       <c r="C207" t="n">
         <v>63.36999893188477</v>
@@ -5936,11 +5948,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>49.15501403808594</v>
+        <v>49.15502166748047</v>
       </c>
       <c r="C208" t="n">
         <v>54.33000183105469</v>
@@ -5965,11 +5977,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>53.12686538696289</v>
+        <v>53.12686157226562</v>
       </c>
       <c r="C209" t="n">
         <v>58.72000122070312</v>
@@ -5994,7 +6006,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6023,11 +6035,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>49.96162796020508</v>
+        <v>49.96162414550781</v>
       </c>
       <c r="C211" t="n">
         <v>54.70000076293945</v>
@@ -6048,11 +6060,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>55.14959335327148</v>
+        <v>55.14959716796875</v>
       </c>
       <c r="C212" t="n">
         <v>60.38000106811523</v>
@@ -6073,11 +6085,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>51.02113342285156</v>
+        <v>51.02113723754883</v>
       </c>
       <c r="C213" t="n">
         <v>55.86000061035156</v>
@@ -6098,7 +6110,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6123,11 +6135,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>45.28148651123047</v>
+        <v>45.281494140625</v>
       </c>
       <c r="C215" t="n">
         <v>49.11000061035156</v>
@@ -6148,7 +6160,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6173,7 +6185,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6198,11 +6210,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>57.91714477539062</v>
+        <v>57.91714096069336</v>
       </c>
       <c r="C218" t="n">
         <v>62.2599983215332</v>
@@ -6223,7 +6235,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6250,11 +6262,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>69.36329650878906</v>
+        <v>69.36328887939453</v>
       </c>
       <c r="C220" t="n">
         <v>74.18000030517578</v>
@@ -6277,7 +6289,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6304,7 +6316,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6331,11 +6343,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>70.79547882080078</v>
+        <v>70.79547119140625</v>
       </c>
       <c r="C223" t="n">
         <v>75.36000061035156</v>
@@ -6358,7 +6370,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6385,11 +6397,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>77.45601654052734</v>
+        <v>77.45602416992188</v>
       </c>
       <c r="C225" t="n">
         <v>82.44999694824219</v>
@@ -6414,11 +6426,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>79.0225830078125</v>
+        <v>79.02259063720703</v>
       </c>
       <c r="C226" t="n">
         <v>83.75</v>
@@ -6443,7 +6455,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6472,11 +6484,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>80.48509979248047</v>
+        <v>80.48508453369141</v>
       </c>
       <c r="C228" t="n">
         <v>85.30000305175781</v>
@@ -6501,7 +6513,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6530,7 +6542,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6559,7 +6571,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6588,11 +6600,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>71.16245269775391</v>
+        <v>71.16244506835938</v>
       </c>
       <c r="C232" t="n">
         <v>74.68000030517578</v>
@@ -6617,11 +6629,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>75.16463470458984</v>
+        <v>75.16462707519531</v>
       </c>
       <c r="C233" t="n">
         <v>78.87999725341797</v>
@@ -6646,7 +6658,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6675,11 +6687,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>77.95719146728516</v>
+        <v>77.95719909667969</v>
       </c>
       <c r="C235" t="n">
         <v>81.41000366210938</v>
@@ -6704,7 +6716,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6733,7 +6745,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6762,7 +6774,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6791,7 +6803,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6820,7 +6832,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6849,7 +6861,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6878,7 +6890,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6907,7 +6919,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6936,7 +6948,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6965,7 +6977,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6994,7 +7006,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7023,7 +7035,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7052,7 +7064,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7081,7 +7093,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7110,32 +7122,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>34.66999816894531</v>
+        <v>34.9900016784668</v>
       </c>
       <c r="C250" t="n">
-        <v>34.66999816894531</v>
+        <v>34.9900016784668</v>
       </c>
       <c r="D250" t="n">
-        <v>100216000</v>
+        <v>105885300</v>
       </c>
       <c r="E250" t="n">
         <v>6.510000000000002</v>
       </c>
       <c r="F250" t="n">
-        <v>5.325652560513871</v>
+        <v>5.374808245540213</v>
       </c>
       <c r="G250" t="n">
         <v>515705917</v>
       </c>
       <c r="H250" t="n">
-        <v>17879523198.10426</v>
+        <v>18044550901.42526</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1943278071792998</v>
+        <v>0.2053210880650028</v>
       </c>
     </row>
   </sheetData>
@@ -7167,75 +7179,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7271,13 +7283,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7313,13 +7325,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7355,13 +7367,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7397,13 +7409,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7439,13 +7451,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7481,13 +7493,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7523,13 +7535,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7565,13 +7577,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7598,7 +7610,7 @@
       <c r="I10" t="n">
         <v>1.15</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7611,13 +7623,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7644,7 +7656,7 @@
       <c r="I11" t="n">
         <v>1.2</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K11" t="n">
@@ -7657,13 +7669,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7690,7 +7702,7 @@
       <c r="I12" t="n">
         <v>1.37</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K12" t="n">
@@ -7703,13 +7715,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7736,7 +7748,7 @@
       <c r="I13" t="n">
         <v>1.48</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K13" t="n">
@@ -7749,13 +7761,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7782,7 +7794,7 @@
       <c r="I14" t="n">
         <v>1.53</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K14" t="n">
@@ -7795,13 +7807,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7828,7 +7840,7 @@
       <c r="I15" t="n">
         <v>1.52</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K15" t="n">
@@ -7841,13 +7853,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7874,7 +7886,7 @@
       <c r="I16" t="n">
         <v>1.62</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K16" t="n">
@@ -7887,13 +7899,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7920,7 +7932,7 @@
       <c r="I17" t="n">
         <v>1.47</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="K17" t="n">
@@ -7933,13 +7945,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7966,7 +7978,7 @@
       <c r="I18" t="n">
         <v>1.55</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="K18" t="n">
@@ -7979,13 +7991,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8012,7 +8024,7 @@
       <c r="I19" t="n">
         <v>1.75</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K19" t="n">
@@ -8025,13 +8037,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8058,7 +8070,7 @@
       <c r="I20" t="n">
         <v>1.61</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K20" t="n">
@@ -8071,13 +8083,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8104,7 +8116,7 @@
       <c r="I21" t="n">
         <v>1.91</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K21" t="n">
@@ -8117,13 +8129,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8150,7 +8162,7 @@
       <c r="I22" t="n">
         <v>1.68</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K22" t="n">
@@ -8163,13 +8175,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8196,7 +8208,7 @@
       <c r="I23" t="n">
         <v>1.72</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K23" t="n">
@@ -8209,13 +8221,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8242,7 +8254,7 @@
       <c r="I24" t="n">
         <v>1.98</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="K24" t="n">
@@ -8255,13 +8267,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8288,7 +8300,7 @@
       <c r="I25" t="n">
         <v>1.91</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="K25" t="n">
@@ -8301,13 +8313,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8334,7 +8346,7 @@
       <c r="I26" t="n">
         <v>2.35</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K26" t="n">
@@ -8347,13 +8359,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8380,7 +8392,7 @@
       <c r="I27" t="n">
         <v>2.21</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K27" t="n">
@@ -8393,13 +8405,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8426,7 +8438,7 @@
       <c r="I28" t="n">
         <v>2.43</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K28" t="n">
@@ -8439,13 +8451,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8472,7 +8484,7 @@
       <c r="I29" t="n">
         <v>2.53</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K29" t="n">
@@ -8485,13 +8497,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8518,7 +8530,7 @@
       <c r="I30" t="n">
         <v>2.19</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K30" t="n">
@@ -8531,13 +8543,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8564,7 +8576,7 @@
       <c r="I31" t="n">
         <v>1.97</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K31" t="n">
@@ -8577,13 +8589,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8610,7 +8622,7 @@
       <c r="I32" t="n">
         <v>1.5</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="K32" t="n">
@@ -8623,13 +8635,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8656,7 +8668,7 @@
       <c r="I33" t="n">
         <v>1.44</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K33" t="n">
@@ -8669,13 +8681,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8702,7 +8714,7 @@
       <c r="I34" t="n">
         <v>1.72</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K34" t="n">
@@ -8715,13 +8727,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8748,7 +8760,7 @@
       <c r="I35" t="n">
         <v>1.96</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K35" t="n">
@@ -8761,13 +8773,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8794,7 +8806,7 @@
       <c r="I36" t="n">
         <v>1.99</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K36" t="n">
@@ -8807,13 +8819,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8840,7 +8852,7 @@
       <c r="I37" t="n">
         <v>1.61</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K37" t="n">
@@ -8853,13 +8865,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8886,7 +8898,7 @@
       <c r="I38" t="n">
         <v>3.930000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K38" t="n">
@@ -8899,13 +8911,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8932,7 +8944,7 @@
       <c r="I39" t="n">
         <v>4.06</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K39" t="n">
@@ -8945,13 +8957,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8978,7 +8990,7 @@
       <c r="I40" t="n">
         <v>4.300000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="K40" t="n">
@@ -8991,13 +9003,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9024,7 +9036,7 @@
       <c r="I41" t="n">
         <v>4.590000000000001</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K41" t="n">
@@ -9037,13 +9049,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9070,7 +9082,7 @@
       <c r="I42" t="n">
         <v>2.55</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K42" t="n">
@@ -9083,13 +9095,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9116,7 +9128,7 @@
       <c r="I43" t="n">
         <v>2.46</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K43" t="n">
@@ -9129,13 +9141,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9162,7 +9174,7 @@
       <c r="I44" t="n">
         <v>2.29</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K44" t="n">
@@ -9175,13 +9187,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9208,7 +9220,7 @@
       <c r="I45" t="n">
         <v>2.11</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K45" t="n">
@@ -9221,13 +9233,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9254,7 +9266,7 @@
       <c r="I46" t="n">
         <v>0.6600000000000004</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K46" t="n">
@@ -9267,13 +9279,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9300,7 +9312,7 @@
       <c r="I47" t="n">
         <v>0.2300000000000005</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K47" t="n">
@@ -9313,13 +9325,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9346,7 +9358,7 @@
       <c r="I48" t="n">
         <v>-0.2099999999999995</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K48" t="n">
@@ -9359,13 +9371,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9392,7 +9404,7 @@
       <c r="I49" t="n">
         <v>-0.4699999999999995</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K49" t="n">
@@ -9405,13 +9417,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9438,7 +9450,7 @@
       <c r="I50" t="n">
         <v>0.2500000000000004</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="K50" t="n">
@@ -9451,13 +9463,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9484,7 +9496,7 @@
       <c r="I51" t="n">
         <v>-0.3699999999999996</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K51" t="n">
@@ -9497,13 +9509,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9530,7 +9542,7 @@
       <c r="I52" t="n">
         <v>0.1500000000000005</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K52" t="n">
@@ -9543,13 +9555,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9576,7 +9588,7 @@
       <c r="I53" t="n">
         <v>0.3800000000000005</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K53" t="n">
@@ -9589,13 +9601,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9622,7 +9634,7 @@
       <c r="I54" t="n">
         <v>0.6700000000000005</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K54" t="n">
@@ -9635,13 +9647,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9668,7 +9680,7 @@
       <c r="I55" t="n">
         <v>1.47</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K55" t="n">
@@ -9681,13 +9693,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9714,7 +9726,7 @@
       <c r="I56" t="n">
         <v>1.370000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K56" t="n">
@@ -9727,13 +9739,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9760,7 +9772,7 @@
       <c r="I57" t="n">
         <v>1.52</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K57" t="n">
@@ -9773,13 +9785,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9815,13 +9827,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9857,13 +9869,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I61" t="n">
         <v>-11.26</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="K61" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I62" t="n">
         <v>-10.25</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="K62" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I63" t="n">
         <v>1.330000000000002</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="K63" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I64" t="n">
         <v>2.500000000000002</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="K64" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I65" t="n">
         <v>2.610000000000002</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K65" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I66" t="n">
         <v>1.510000000000002</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K66" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I67" t="n">
         <v>0.1700000000000016</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K67" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I68" t="n">
         <v>0.2600000000000016</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K68" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I69" t="n">
         <v>0.7300000000000018</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K69" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I70" t="n">
         <v>5.160000000000002</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="K70" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I71" t="n">
         <v>6.510000000000002</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K71" t="n">
@@ -10429,52 +10441,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="C2" t="n">
@@ -10503,10 +10515,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10535,10 +10547,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10567,10 +10579,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40303</v>
       </c>
       <c r="C5" t="n">
@@ -10599,10 +10611,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="C6" t="n">
@@ -10631,10 +10643,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10663,10 +10675,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10695,10 +10707,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10727,10 +10739,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10791,10 +10803,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10823,10 +10835,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C13" t="n">
@@ -10855,10 +10867,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C14" t="n">
@@ -10887,10 +10899,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41220</v>
       </c>
       <c r="C15" t="n">
@@ -10919,10 +10931,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="C16" t="n">
@@ -10951,10 +10963,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C17" t="n">
@@ -10983,10 +10995,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C18" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C19" t="n">
@@ -11047,10 +11059,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C20" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C21" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41858</v>
       </c>
       <c r="C22" t="n">
@@ -11143,10 +11155,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C23" t="n">
@@ -11175,10 +11187,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C24" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C25" t="n">
@@ -11239,10 +11251,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C26" t="n">
@@ -11271,10 +11283,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C27" t="n">
@@ -11303,10 +11315,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C28" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11367,10 +11379,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="C30" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="C31" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11495,10 +11507,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C34" t="n">
@@ -11527,10 +11539,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C35" t="n">
@@ -11559,10 +11571,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C36" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43311</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C38" t="n">
@@ -11655,10 +11667,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C39" t="n">
@@ -11687,10 +11699,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43515</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C40" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43584</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C41" t="n">
@@ -11751,10 +11763,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43682</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C42" t="n">
@@ -11783,10 +11795,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43773</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C43" t="n">
@@ -11815,10 +11827,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C44" t="n">
@@ -11847,10 +11859,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43957</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C45" t="n">
@@ -11879,10 +11891,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44046</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C46" t="n">
@@ -11911,10 +11923,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44132</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C47" t="n">
@@ -11943,10 +11955,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44244</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="C48" t="n">
@@ -11975,10 +11987,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44321</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C49" t="n">
@@ -12007,10 +12019,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C50" t="n">
@@ -12039,10 +12051,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44503</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C51" t="n">
@@ -12071,10 +12083,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44613</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C52" t="n">
@@ -12103,10 +12115,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C53" t="n">
@@ -12135,10 +12147,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44776</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C54" t="n">
@@ -12167,10 +12179,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44867</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C55" t="n">
@@ -12199,10 +12211,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44979</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C56" t="n">
@@ -12231,10 +12243,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C57" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45233</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="C59" t="n">
@@ -12327,10 +12339,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45344</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="C60" t="n">
@@ -12359,10 +12371,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45415</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C61" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45506</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="C62" t="n">
@@ -12423,10 +12435,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="C63" t="n">
@@ -12455,10 +12467,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45699</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C64" t="n">
@@ -12487,10 +12499,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45779</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C65" t="n">
@@ -12519,10 +12531,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C66" t="n">
@@ -12551,10 +12563,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C67" t="n">
@@ -12583,10 +12595,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C68" t="n">
@@ -12615,10 +12627,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46148</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="C69" t="n">
@@ -12647,10 +12659,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C70" t="n">
@@ -12697,12 +12709,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/FIS.xlsx
+++ b/salidas/empresas/FIS.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>16.02048301696777</v>
+        <v>16.02048110961914</v>
       </c>
       <c r="C2" t="n">
         <v>43.45000076293945</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.00030899047852</v>
+        <v>16.00031280517578</v>
       </c>
       <c r="C3" t="n">
         <v>39.65000152587891</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>16.38400077819824</v>
+        <v>16.38399887084961</v>
       </c>
       <c r="C4" t="n">
         <v>40.54999923706055</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>15.35368347167969</v>
+        <v>15.353684425354</v>
       </c>
       <c r="C5" t="n">
         <v>38</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>14.84458637237549</v>
+        <v>14.84458255767822</v>
       </c>
       <c r="C6" t="n">
         <v>36.7400016784668</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>14.32334041595459</v>
+        <v>14.32334327697754</v>
       </c>
       <c r="C7" t="n">
         <v>35.40000152587891</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>14.46091842651367</v>
+        <v>14.46091461181641</v>
       </c>
       <c r="C8" t="n">
         <v>35.7400016784668</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.82507038116455</v>
+        <v>14.82506847381592</v>
       </c>
       <c r="C9" t="n">
         <v>36.63999938964844</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.9910831451416</v>
+        <v>14.99109745025635</v>
       </c>
       <c r="C10" t="n">
         <v>37</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>16.84268569946289</v>
+        <v>16.84269142150879</v>
       </c>
       <c r="C11" t="n">
         <v>41.56999969482422</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>16.16607093811035</v>
+        <v>16.16606521606445</v>
       </c>
       <c r="C12" t="n">
         <v>39.90000152587891</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>16.26308631896973</v>
+        <v>16.26309585571289</v>
       </c>
       <c r="C13" t="n">
         <v>40.09000015258789</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>17.24885559082031</v>
+        <v>17.24886131286621</v>
       </c>
       <c r="C14" t="n">
         <v>42.52000045776367</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>18.62811279296875</v>
+        <v>18.62812232971191</v>
       </c>
       <c r="C15" t="n">
         <v>45.91999816894531</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>18.46187782287598</v>
+        <v>18.46187973022461</v>
       </c>
       <c r="C16" t="n">
         <v>45.45999908447266</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>21.89759254455566</v>
+        <v>21.8975944519043</v>
       </c>
       <c r="C18" t="n">
         <v>53.91999816894531</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>22.06480598449707</v>
+        <v>22.06478881835938</v>
       </c>
       <c r="C19" t="n">
         <v>54.27999877929688</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>20.1745662689209</v>
+        <v>20.17457580566406</v>
       </c>
       <c r="C20" t="n">
         <v>49.63000106811523</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>19.26807975769043</v>
+        <v>19.2680835723877</v>
       </c>
       <c r="C21" t="n">
         <v>47.40000152587891</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>18.05658531188965</v>
+        <v>18.05658912658691</v>
       </c>
       <c r="C22" t="n">
         <v>44.36999893188477</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>18.75248336791992</v>
+        <v>18.75247764587402</v>
       </c>
       <c r="C23" t="n">
         <v>46.08000183105469</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.58859252929688</v>
+        <v>17.58858680725098</v>
       </c>
       <c r="C24" t="n">
         <v>43.22000122070312</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>16.94395637512207</v>
+        <v>16.9439582824707</v>
       </c>
       <c r="C25" t="n">
         <v>41.59000015258789</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>17.28209495544434</v>
+        <v>17.2820987701416</v>
       </c>
       <c r="C26" t="n">
         <v>42.41999816894531</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>16.90321731567383</v>
+        <v>16.90322303771973</v>
       </c>
       <c r="C27" t="n">
         <v>41.4900016784668</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.55872631072998</v>
+        <v>15.5587329864502</v>
       </c>
       <c r="C28" t="n">
         <v>38.13999938964844</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>14.71021842956543</v>
+        <v>14.7102165222168</v>
       </c>
       <c r="C29" t="n">
         <v>36.06000137329102</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>16.43171119689941</v>
+        <v>16.43171501159668</v>
       </c>
       <c r="C30" t="n">
         <v>40.27999877929688</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.07626152038574</v>
+        <v>15.07625579833984</v>
       </c>
       <c r="C31" t="n">
         <v>36.90999984741211</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>13.89526748657227</v>
+        <v>13.89527225494385</v>
       </c>
       <c r="C32" t="n">
         <v>18.95000076293945</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>16.02172660827637</v>
+        <v>16.02171516418457</v>
       </c>
       <c r="C33" t="n">
         <v>21.85000038146973</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>13.56740760803223</v>
+        <v>13.56740665435791</v>
       </c>
       <c r="C34" t="n">
         <v>18.45999908447266</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>11.09057712554932</v>
+        <v>11.0905818939209</v>
       </c>
       <c r="C35" t="n">
         <v>15.09000015258789</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>12.62665367126465</v>
+        <v>12.62665271759033</v>
       </c>
       <c r="C36" t="n">
         <v>17.18000030517578</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.72861862182617</v>
+        <v>11.72861957550049</v>
       </c>
       <c r="C38" t="n">
         <v>15.90999984741211</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>12.90074634552002</v>
+        <v>12.90074825286865</v>
       </c>
       <c r="C39" t="n">
         <v>17.5</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>13.45748329162598</v>
+        <v>13.45748138427734</v>
       </c>
       <c r="C40" t="n">
         <v>18.20000076293945</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>13.19868564605713</v>
+        <v>13.19868183135986</v>
       </c>
       <c r="C41" t="n">
         <v>17.85000038146973</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.24127292633057</v>
+        <v>14.24127101898193</v>
       </c>
       <c r="C42" t="n">
         <v>19.26000022888184</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.79530429840088</v>
+        <v>14.79530048370361</v>
       </c>
       <c r="C43" t="n">
         <v>19.95999908447266</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.36001968383789</v>
+        <v>17.36002731323242</v>
       </c>
       <c r="C44" t="n">
         <v>23.42000007629395</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>18.20504951477051</v>
+        <v>18.20504570007324</v>
       </c>
       <c r="C45" t="n">
         <v>24.55999946594238</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>18.94740676879883</v>
+        <v>18.94740295410156</v>
       </c>
       <c r="C46" t="n">
         <v>25.51000022888184</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.1621036529541</v>
+        <v>16.16211318969727</v>
       </c>
       <c r="C47" t="n">
         <v>21.76000022888184</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>16.78601837158203</v>
+        <v>16.78601455688477</v>
       </c>
       <c r="C48" t="n">
         <v>22.60000038146973</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.44668388366699</v>
+        <v>17.44668006896973</v>
       </c>
       <c r="C49" t="n">
         <v>23.44000053405762</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.77679824829102</v>
+        <v>16.77680397033691</v>
       </c>
       <c r="C51" t="n">
         <v>22.54000091552734</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>17.48437118530273</v>
+        <v>17.48435974121094</v>
       </c>
       <c r="C52" t="n">
         <v>23.44000053405762</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>19.61023712158203</v>
+        <v>19.61023139953613</v>
       </c>
       <c r="C53" t="n">
         <v>26.29000091552734</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>20.04239654541016</v>
+        <v>20.04239845275879</v>
       </c>
       <c r="C55" t="n">
         <v>26.81999969482422</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>21.42489051818848</v>
+        <v>21.42489433288574</v>
       </c>
       <c r="C56" t="n">
         <v>28.67000007629395</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>19.31752967834473</v>
+        <v>19.31752395629883</v>
       </c>
       <c r="C57" t="n">
         <v>25.85000038146973</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>20.31076622009277</v>
+        <v>20.31076431274414</v>
       </c>
       <c r="C58" t="n">
         <v>27.1299991607666</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>20.28830337524414</v>
+        <v>20.28831100463867</v>
       </c>
       <c r="C59" t="n">
         <v>27.10000038146973</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.13857650756836</v>
+        <v>20.13857460021973</v>
       </c>
       <c r="C60" t="n">
         <v>26.89999961853027</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.54236602783203</v>
+        <v>20.54235649108887</v>
       </c>
       <c r="C61" t="n">
         <v>27.38999938964844</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>22.82234191894531</v>
+        <v>22.82235145568848</v>
       </c>
       <c r="C62" t="n">
         <v>30.43000030517578</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>24.29232978820801</v>
+        <v>24.29232788085938</v>
       </c>
       <c r="C63" t="n">
         <v>32.38999938964844</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>24.55695724487305</v>
+        <v>24.55694961547852</v>
       </c>
       <c r="C64" t="n">
         <v>32.68999862670898</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>24.87245941162109</v>
+        <v>24.87246513366699</v>
       </c>
       <c r="C65" t="n">
         <v>33.11000061035156</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>24.17384338378906</v>
+        <v>24.17384147644043</v>
       </c>
       <c r="C66" t="n">
         <v>32.18000030517578</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>22.58721351623535</v>
+        <v>22.58720970153809</v>
       </c>
       <c r="C68" t="n">
         <v>30.02000045776367</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>21.20278167724609</v>
+        <v>21.20277976989746</v>
       </c>
       <c r="C69" t="n">
         <v>28.18000030517578</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>18.33437728881836</v>
+        <v>18.33438491821289</v>
       </c>
       <c r="C70" t="n">
         <v>24.31999969482422</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>19.73660278320312</v>
+        <v>19.73659515380859</v>
       </c>
       <c r="C71" t="n">
         <v>26.18000030517578</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>20.08549880981445</v>
+        <v>20.08549308776855</v>
       </c>
       <c r="C73" t="n">
         <v>26.59000015258789</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>21.57358360290527</v>
+        <v>21.5735912322998</v>
       </c>
       <c r="C74" t="n">
         <v>28.55999946594238</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>23.96813201904297</v>
+        <v>23.9681339263916</v>
       </c>
       <c r="C75" t="n">
         <v>31.72999954223633</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>25.59317779541016</v>
+        <v>25.59317398071289</v>
       </c>
       <c r="C77" t="n">
         <v>33.66999816894531</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>24.91667556762695</v>
+        <v>24.91666984558105</v>
       </c>
       <c r="C78" t="n">
         <v>32.77999877929688</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>26.06722831726074</v>
+        <v>26.06723785400391</v>
       </c>
       <c r="C79" t="n">
         <v>34.08000183105469</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>24.09384536743164</v>
+        <v>24.09383583068848</v>
       </c>
       <c r="C81" t="n">
         <v>31.5</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.03005027770996</v>
+        <v>24.0300464630127</v>
       </c>
       <c r="C82" t="n">
         <v>31.21999931335449</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.300048828125</v>
+        <v>25.30004501342773</v>
       </c>
       <c r="C83" t="n">
         <v>32.86999893188477</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>27.78618621826172</v>
+        <v>27.78617858886719</v>
       </c>
       <c r="C84" t="n">
         <v>36.09999847412109</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>26.94147109985352</v>
+        <v>26.94146728515625</v>
       </c>
       <c r="C85" t="n">
         <v>34.81000137329102</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>28.72156715393066</v>
+        <v>28.72156524658203</v>
       </c>
       <c r="C86" t="n">
         <v>37.11000061035156</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>29.13950538635254</v>
+        <v>29.1395092010498</v>
       </c>
       <c r="C87" t="n">
         <v>37.65000152587891</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>30.84051704406738</v>
+        <v>30.84052276611328</v>
       </c>
       <c r="C88" t="n">
         <v>39.61999893188477</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>32.7320442199707</v>
+        <v>32.73204803466797</v>
       </c>
       <c r="C89" t="n">
         <v>42.04999923706055</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>34.95051574707031</v>
+        <v>34.95050811767578</v>
       </c>
       <c r="C90" t="n">
         <v>44.90000152587891</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>33.51237869262695</v>
+        <v>33.51237487792969</v>
       </c>
       <c r="C91" t="n">
         <v>42.84000015258789</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>34.77965545654297</v>
+        <v>34.7796630859375</v>
       </c>
       <c r="C93" t="n">
         <v>44.45999908447266</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>36.50372695922852</v>
+        <v>36.50374221801758</v>
       </c>
       <c r="C94" t="n">
         <v>46.43999862670898</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>39.83655548095703</v>
+        <v>39.83656311035156</v>
       </c>
       <c r="C96" t="n">
         <v>50.68000030517578</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>42.37929153442383</v>
+        <v>42.37929534912109</v>
       </c>
       <c r="C97" t="n">
         <v>53.68000030517578</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>40.02663803100586</v>
+        <v>40.02664566040039</v>
       </c>
       <c r="C98" t="n">
         <v>50.70000076293945</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>43.90299224853516</v>
+        <v>43.90298843383789</v>
       </c>
       <c r="C99" t="n">
         <v>55.61000061035156</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>42.38351058959961</v>
+        <v>42.38349533081055</v>
       </c>
       <c r="C100" t="n">
         <v>53.45000076293945</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>42.36766815185547</v>
+        <v>42.36763763427734</v>
       </c>
       <c r="C101" t="n">
         <v>53.43000030517578</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>42.93857955932617</v>
+        <v>42.93859481811523</v>
       </c>
       <c r="C102" t="n">
         <v>54.15000152587891</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>43.59866333007812</v>
+        <v>43.59865570068359</v>
       </c>
       <c r="C103" t="n">
         <v>54.7400016784668</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>44.92079925537109</v>
+        <v>44.92080307006836</v>
       </c>
       <c r="C104" t="n">
         <v>56.40000152587891</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>45.19956970214844</v>
+        <v>45.19955444335938</v>
       </c>
       <c r="C105" t="n">
         <v>56.75</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>45.02913665771484</v>
+        <v>45.02914047241211</v>
       </c>
       <c r="C106" t="n">
         <v>56.29999923706055</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>46.70071411132812</v>
+        <v>46.70071029663086</v>
       </c>
       <c r="C107" t="n">
         <v>58.38999938964844</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>48.94018173217773</v>
+        <v>48.94019317626953</v>
       </c>
       <c r="C108" t="n">
         <v>61.18999862670898</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>49.94453048706055</v>
+        <v>49.94452285766602</v>
       </c>
       <c r="C109" t="n">
         <v>62.20000076293945</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>50.12921524047852</v>
+        <v>50.12920761108398</v>
       </c>
       <c r="C110" t="n">
         <v>62.43000030517578</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.27250289916992</v>
+        <v>54.27252578735352</v>
       </c>
       <c r="C111" t="n">
         <v>67.58999633789062</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>54.865234375</v>
+        <v>54.8652229309082</v>
       </c>
       <c r="C112" t="n">
         <v>68.05999755859375</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>50.37508773803711</v>
+        <v>50.37509155273438</v>
       </c>
       <c r="C113" t="n">
         <v>62.4900016784668</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>50.54437637329102</v>
+        <v>50.54438018798828</v>
       </c>
       <c r="C114" t="n">
         <v>62.70000076293945</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>50.02156829833984</v>
+        <v>50.02156066894531</v>
       </c>
       <c r="C115" t="n">
         <v>61.79999923706055</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>52.9597282409668</v>
+        <v>52.95971298217773</v>
       </c>
       <c r="C116" t="n">
         <v>65.43000030517578</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>55.89786911010742</v>
+        <v>55.89788055419922</v>
       </c>
       <c r="C117" t="n">
         <v>69.05999755859375</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>54.49877548217773</v>
+        <v>54.49879455566406</v>
       </c>
       <c r="C118" t="n">
         <v>67.08000183105469</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>59.24346160888672</v>
+        <v>59.24344253540039</v>
       </c>
       <c r="C119" t="n">
         <v>72.91999816894531</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>51.72834777832031</v>
+        <v>51.72835159301758</v>
       </c>
       <c r="C120" t="n">
         <v>63.66999816894531</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.44418334960938</v>
+        <v>49.44419860839844</v>
       </c>
       <c r="C121" t="n">
         <v>60.59999847412109</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>48.73435592651367</v>
+        <v>48.73434448242188</v>
       </c>
       <c r="C122" t="n">
         <v>59.72999954223633</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>47.52680206298828</v>
+        <v>47.52679061889648</v>
       </c>
       <c r="C123" t="n">
         <v>58.25</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>51.87006378173828</v>
+        <v>51.87007522583008</v>
       </c>
       <c r="C124" t="n">
         <v>63.31000137329102</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>53.9101448059082</v>
+        <v>53.91012954711914</v>
       </c>
       <c r="C125" t="n">
         <v>65.80000305175781</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>60.849609375</v>
+        <v>60.8496208190918</v>
       </c>
       <c r="C126" t="n">
         <v>74.26999664306641</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>60.58073043823242</v>
+        <v>60.58072280883789</v>
       </c>
       <c r="C127" t="n">
         <v>73.68000030517578</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>65.39067840576172</v>
+        <v>65.39065551757812</v>
       </c>
       <c r="C128" t="n">
         <v>79.52999877929688</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>65.22621917724609</v>
+        <v>65.22622680664062</v>
       </c>
       <c r="C129" t="n">
         <v>79.33000183105469</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>63.55055236816406</v>
+        <v>63.55057144165039</v>
       </c>
       <c r="C130" t="n">
         <v>77.02999877929688</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>60.98480606079102</v>
+        <v>60.98480987548828</v>
       </c>
       <c r="C131" t="n">
         <v>73.91999816894531</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>63.68255996704102</v>
+        <v>63.68257904052734</v>
       </c>
       <c r="C132" t="n">
         <v>77.19000244140625</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>62.61992263793945</v>
+        <v>62.61993789672852</v>
       </c>
       <c r="C133" t="n">
         <v>75.63999938964844</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>65.74928283691406</v>
+        <v>65.74925994873047</v>
       </c>
       <c r="C134" t="n">
         <v>79.41999816894531</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>68.10868835449219</v>
+        <v>68.10869598388672</v>
       </c>
       <c r="C135" t="n">
         <v>82.26999664306641</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>66.14746856689453</v>
+        <v>66.14747619628906</v>
       </c>
       <c r="C136" t="n">
         <v>79.62000274658203</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>71.33992767333984</v>
+        <v>71.33990478515625</v>
       </c>
       <c r="C138" t="n">
         <v>85.87000274658203</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>71.19021606445312</v>
+        <v>71.19023132324219</v>
       </c>
       <c r="C139" t="n">
         <v>85.40000152587891</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>76.04184722900391</v>
+        <v>76.04183197021484</v>
       </c>
       <c r="C140" t="n">
         <v>91.22000122070312</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>77.45893859863281</v>
+        <v>77.45895385742188</v>
       </c>
       <c r="C141" t="n">
         <v>92.91999816894531</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>78.09580993652344</v>
+        <v>78.09579467773438</v>
       </c>
       <c r="C142" t="n">
         <v>93.38999938964844</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>77.56898498535156</v>
+        <v>77.5689697265625</v>
       </c>
       <c r="C143" t="n">
         <v>92.76000213623047</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>78.88185882568359</v>
+        <v>78.88188171386719</v>
       </c>
       <c r="C144" t="n">
         <v>94.33000183105469</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.92399597167969</v>
+        <v>78.92397308349609</v>
       </c>
       <c r="C145" t="n">
         <v>94.08999633789062</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>81.51591491699219</v>
+        <v>81.51590728759766</v>
       </c>
       <c r="C147" t="n">
         <v>97.18000030517578</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>81.03627014160156</v>
+        <v>81.03624725341797</v>
       </c>
       <c r="C148" t="n">
         <v>96.30000305175781</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>86.01793670654297</v>
+        <v>86.01792144775391</v>
       </c>
       <c r="C150" t="n">
         <v>102.2200012207031</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>89.49140930175781</v>
+        <v>89.49141693115234</v>
       </c>
       <c r="C151" t="n">
         <v>106.0299987792969</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>87.04375457763672</v>
+        <v>87.04374694824219</v>
       </c>
       <c r="C152" t="n">
         <v>103.129997253418</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>91.29761505126953</v>
+        <v>91.297607421875</v>
       </c>
       <c r="C153" t="n">
         <v>108.1699981689453</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>92.3270263671875</v>
+        <v>92.32706451416016</v>
       </c>
       <c r="C154" t="n">
         <v>109.0699996948242</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>88.11997985839844</v>
+        <v>88.11995697021484</v>
       </c>
       <c r="C155" t="n">
         <v>104.0999984741211</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>91.37896728515625</v>
+        <v>91.37895965576172</v>
       </c>
       <c r="C156" t="n">
         <v>107.9499969482422</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>88.75001525878906</v>
+        <v>88.75003051757812</v>
       </c>
       <c r="C158" t="n">
         <v>104.5299987792969</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>91.82356262207031</v>
+        <v>91.82355499267578</v>
       </c>
       <c r="C159" t="n">
         <v>108.1500015258789</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>96.33966064453125</v>
+        <v>96.33967590332031</v>
       </c>
       <c r="C160" t="n">
         <v>113.0999984741211</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>98.75028228759766</v>
+        <v>98.75030517578125</v>
       </c>
       <c r="C161" t="n">
         <v>115.9300003051758</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>102.4727020263672</v>
+        <v>102.4727249145508</v>
       </c>
       <c r="C162" t="n">
         <v>120.3000030517578</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>104.8032913208008</v>
+        <v>104.8032684326172</v>
       </c>
       <c r="C163" t="n">
         <v>122.6800003051758</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>113.8330307006836</v>
+        <v>113.8330078125</v>
       </c>
       <c r="C164" t="n">
         <v>133.25</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>116.3702621459961</v>
+        <v>116.3702774047852</v>
       </c>
       <c r="C165" t="n">
         <v>136.2200012207031</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>113.7175979614258</v>
+        <v>113.7175750732422</v>
       </c>
       <c r="C166" t="n">
         <v>132.7599945068359</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>112.8610382080078</v>
+        <v>112.8610229492188</v>
       </c>
       <c r="C167" t="n">
         <v>131.7599945068359</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>119.4481811523438</v>
+        <v>119.4481887817383</v>
       </c>
       <c r="C169" t="n">
         <v>139.0899963378906</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>123.3728256225586</v>
+        <v>123.3728866577148</v>
       </c>
       <c r="C170" t="n">
         <v>143.6600036621094</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>119.9892272949219</v>
+        <v>119.9892425537109</v>
       </c>
       <c r="C171" t="n">
         <v>139.7200012207031</v>
@@ -4984,7 +4984,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>119.5395736694336</v>
+        <v>119.5395812988281</v>
       </c>
       <c r="C174" t="n">
         <v>138.8300018310547</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>115.7450637817383</v>
+        <v>115.7450714111328</v>
       </c>
       <c r="C175" t="n">
         <v>134.0899963378906</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>126.2932586669922</v>
+        <v>126.2932281494141</v>
       </c>
       <c r="C176" t="n">
         <v>146.3099975585938</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>130.212158203125</v>
+        <v>130.2121734619141</v>
       </c>
       <c r="C177" t="n">
         <v>150.8500061035156</v>
@@ -5179,7 +5179,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>122.686408996582</v>
+        <v>122.6864013671875</v>
       </c>
       <c r="C181" t="n">
         <v>141.4600067138672</v>
@@ -5206,7 +5206,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>107.0752716064453</v>
+        <v>107.0752639770508</v>
       </c>
       <c r="C182" t="n">
         <v>123.4599990844727</v>
@@ -5233,7 +5233,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>119.6856231689453</v>
+        <v>119.6856079101562</v>
       </c>
       <c r="C183" t="n">
         <v>138</v>
@@ -5262,7 +5262,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>122.2769393920898</v>
+        <v>122.2769317626953</v>
       </c>
       <c r="C184" t="n">
         <v>140.6100006103516</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>132.9645385742188</v>
+        <v>132.9645080566406</v>
       </c>
       <c r="C185" t="n">
         <v>152.8999938964844</v>
@@ -5320,7 +5320,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>129.5556335449219</v>
+        <v>129.5556488037109</v>
       </c>
       <c r="C186" t="n">
         <v>148.9799957275391</v>
@@ -5347,7 +5347,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>123.5307159423828</v>
+        <v>123.5306777954102</v>
       </c>
       <c r="C187" t="n">
         <v>141.6699981689453</v>
@@ -5374,7 +5374,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>129.9657592773438</v>
+        <v>129.9658050537109</v>
       </c>
       <c r="C188" t="n">
         <v>149.0500030517578</v>
@@ -5401,7 +5401,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>111.4104385375977</v>
+        <v>111.4104461669922</v>
       </c>
       <c r="C189" t="n">
         <v>127.7699966430664</v>
@@ -5430,7 +5430,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>106.4194641113281</v>
+        <v>106.4194564819336</v>
       </c>
       <c r="C190" t="n">
         <v>121.6800003051758</v>
@@ -5459,7 +5459,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>96.85149383544922</v>
+        <v>96.85150146484375</v>
       </c>
       <c r="C191" t="n">
         <v>110.7399978637695</v>
@@ -5488,7 +5488,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>91.39411163330078</v>
+        <v>91.39408874511719</v>
       </c>
       <c r="C192" t="n">
         <v>104.5</v>
@@ -5517,7 +5517,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>95.81684875488281</v>
+        <v>95.81682586669922</v>
       </c>
       <c r="C193" t="n">
         <v>109.1500015258789</v>
@@ -5604,7 +5604,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>88.60599517822266</v>
+        <v>88.60600280761719</v>
       </c>
       <c r="C196" t="n">
         <v>100.4199981689453</v>
@@ -5691,7 +5691,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>81.25347137451172</v>
+        <v>81.25345611572266</v>
       </c>
       <c r="C199" t="n">
         <v>91.66999816894531</v>
@@ -5720,7 +5720,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>90.55146026611328</v>
+        <v>90.55148315429688</v>
       </c>
       <c r="C200" t="n">
         <v>102.1600036621094</v>
@@ -5749,7 +5749,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>80.987548828125</v>
+        <v>80.98754119873047</v>
       </c>
       <c r="C201" t="n">
         <v>91.37000274658203</v>
@@ -5923,7 +5923,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>56.86010360717773</v>
+        <v>56.86011505126953</v>
       </c>
       <c r="C207" t="n">
         <v>63.36999893188477</v>
@@ -5952,7 +5952,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>49.15502166748047</v>
+        <v>49.1550178527832</v>
       </c>
       <c r="C208" t="n">
         <v>54.33000183105469</v>
@@ -5981,7 +5981,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>53.12686157226562</v>
+        <v>53.12686920166016</v>
       </c>
       <c r="C209" t="n">
         <v>58.72000122070312</v>
@@ -6010,7 +6010,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>49.37215805053711</v>
+        <v>49.37216186523438</v>
       </c>
       <c r="C210" t="n">
         <v>54.56999969482422</v>
@@ -6039,7 +6039,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>49.96162414550781</v>
+        <v>49.96161651611328</v>
       </c>
       <c r="C211" t="n">
         <v>54.70000076293945</v>
@@ -6064,7 +6064,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>55.14959716796875</v>
+        <v>55.14960098266602</v>
       </c>
       <c r="C212" t="n">
         <v>60.38000106811523</v>
@@ -6114,7 +6114,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>50.96127700805664</v>
+        <v>50.96126937866211</v>
       </c>
       <c r="C214" t="n">
         <v>55.27000045776367</v>
@@ -6139,7 +6139,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>45.281494140625</v>
+        <v>45.2814826965332</v>
       </c>
       <c r="C215" t="n">
         <v>49.11000061035156</v>
@@ -6164,7 +6164,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>54.06855392456055</v>
+        <v>54.06855773925781</v>
       </c>
       <c r="C216" t="n">
         <v>58.63999938964844</v>
@@ -6214,7 +6214,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>57.91714096069336</v>
+        <v>57.91714477539062</v>
       </c>
       <c r="C218" t="n">
         <v>62.2599983215332</v>
@@ -6293,7 +6293,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>63.50975036621094</v>
+        <v>63.509765625</v>
       </c>
       <c r="C221" t="n">
         <v>67.91999816894531</v>
@@ -6320,7 +6320,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>70.95289611816406</v>
+        <v>70.95288848876953</v>
       </c>
       <c r="C222" t="n">
         <v>75.87999725341797</v>
@@ -6347,7 +6347,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>70.79547119140625</v>
+        <v>70.79548645019531</v>
       </c>
       <c r="C223" t="n">
         <v>75.36000061035156</v>
@@ -6401,7 +6401,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>77.45602416992188</v>
+        <v>77.45603942871094</v>
       </c>
       <c r="C225" t="n">
         <v>82.44999694824219</v>
@@ -6488,7 +6488,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>80.48508453369141</v>
+        <v>80.48509979248047</v>
       </c>
       <c r="C228" t="n">
         <v>85.30000305175781</v>
@@ -6517,7 +6517,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>76.53363800048828</v>
+        <v>76.53364562988281</v>
       </c>
       <c r="C229" t="n">
         <v>80.76999664306641</v>
@@ -6546,7 +6546,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>77.19692230224609</v>
+        <v>77.19693756103516</v>
       </c>
       <c r="C230" t="n">
         <v>81.47000122070312</v>
@@ -6575,7 +6575,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>67.38978576660156</v>
+        <v>67.38979339599609</v>
       </c>
       <c r="C231" t="n">
         <v>71.12000274658203</v>
@@ -6604,7 +6604,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>71.16244506835938</v>
+        <v>71.16246032714844</v>
       </c>
       <c r="C232" t="n">
         <v>74.68000030517578</v>
@@ -6633,7 +6633,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>75.16462707519531</v>
+        <v>75.16463470458984</v>
       </c>
       <c r="C233" t="n">
         <v>78.87999725341797</v>
@@ -6691,7 +6691,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>77.95719909667969</v>
+        <v>77.95718383789062</v>
       </c>
       <c r="C235" t="n">
         <v>81.41000366210938</v>
@@ -6749,7 +6749,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>66.84916687011719</v>
+        <v>66.84915924072266</v>
       </c>
       <c r="C237" t="n">
         <v>69.80999755859375</v>
@@ -6778,7 +6778,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>63.51343154907227</v>
+        <v>63.513427734375</v>
       </c>
       <c r="C238" t="n">
         <v>65.94000244140625</v>
@@ -6807,7 +6807,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>60.21928787231445</v>
+        <v>60.21928405761719</v>
       </c>
       <c r="C239" t="n">
         <v>62.52000045776367</v>
@@ -6836,7 +6836,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>63.34968566894531</v>
+        <v>63.34968185424805</v>
       </c>
       <c r="C240" t="n">
         <v>65.76999664306641</v>
@@ -6894,7 +6894,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>53.54190826416016</v>
+        <v>53.54190444946289</v>
       </c>
       <c r="C242" t="n">
         <v>55.25</v>
@@ -7010,7 +7010,7 @@
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>42.01910018920898</v>
+        <v>42.01909637451172</v>
       </c>
       <c r="C246" t="n">
         <v>42.9900016784668</v>
